--- a/wwwroot/test.xlsx
+++ b/wwwroot/test.xlsx
@@ -8,14 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Carbon-inventory-platform\wwwroot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB7DA00-A41F-4D1F-A9A9-5DAB25EFBEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FCBEEE5-AD9F-48B1-BC93-B5277F34E7DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="727" yWindow="2168" windowWidth="14220" windowHeight="7830" xr2:uid="{B6C6FE3C-00CF-427C-BF72-AD6EBFF9061C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" xr2:uid="{B6C6FE3C-00CF-427C-BF72-AD6EBFF9061C}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
-    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
+    <sheet name="邊界資料" sheetId="4" r:id="rId1"/>
+    <sheet name="排放源資料" sheetId="1" r:id="rId2"/>
+    <sheet name="排放量計算資料" sheetId="2" r:id="rId3"/>
+    <sheet name="溫室氣體排放量彙總" sheetId="3" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="縣市別">[1]附表三!$E$3:$E$25</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="113">
   <si>
     <t>原燃物料</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,81 +71,489 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>儀器校正等級</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排放係數誤差等級</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>數據等級評分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活動數據信賴區間上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活動數據信賴區間下限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CO2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CH4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N2O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HFCS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PFCS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NF3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>溫室氣體</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排放係數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GWP值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排放係數不確性上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排放係數不確性下限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>單位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000080"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>地址</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000080"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>姓名</t>
+    </r>
+  </si>
+  <si>
+    <t>工廠登記編號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電話號碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>產業別</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>統一編號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電子信箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盤查年度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HFCs</t>
+  </si>
+  <si>
+    <t>PFCs</t>
+  </si>
+  <si>
+    <t>SF6</t>
+  </si>
+  <si>
+    <t>範疇一七種溫室氣體年總排放當量</t>
+  </si>
+  <si>
+    <t>進行不確定性評估之排放量絕對值加總</t>
+  </si>
+  <si>
+    <t>排放總量絕對值加總</t>
+  </si>
+  <si>
+    <t>[第1級個數]</t>
+  </si>
+  <si>
+    <t>[第2級個數]</t>
+  </si>
+  <si>
+    <t>[第3級個數]</t>
+  </si>
+  <si>
+    <t>[清冊等級分數]</t>
+  </si>
+  <si>
+    <t>[清冊級別]</t>
+  </si>
+  <si>
+    <t>全廠七大溫室氣體排放量統計表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>範疇一七大溫室氣體排放量統計表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全廠溫室氣體範疇別及範疇一排放型式排放量統計表</t>
+  </si>
+  <si>
+    <t>溫室氣體不確定性量化評估結果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全廠溫室氣體數據等級評分結果</t>
+  </si>
+  <si>
+    <t>總排放當量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CO</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CH</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SF</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>NF</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <t>[CO2排放]</t>
+  </si>
+  <si>
+    <t>[CH4排放]</t>
+  </si>
+  <si>
+    <t>[N2O排放]</t>
+  </si>
+  <si>
+    <t>[HFCS排放]</t>
+  </si>
+  <si>
+    <t>[PFCS排放]</t>
+  </si>
+  <si>
+    <t>[SF6排放]</t>
+  </si>
+  <si>
+    <t>[NF3排放]</t>
+  </si>
+  <si>
+    <t>[類別一CO2排放]</t>
+  </si>
+  <si>
+    <t>[類別一CH4排放]</t>
+  </si>
+  <si>
+    <t>[類別一N2O排放]</t>
+  </si>
+  <si>
+    <t>[類別一HFCS排放]</t>
+  </si>
+  <si>
+    <t>[類別一PFCS排放]</t>
+  </si>
+  <si>
+    <t>[類別一SF6排放]</t>
+  </si>
+  <si>
+    <t>[類別一NF3排放]</t>
+  </si>
+  <si>
+    <t>範疇1</t>
+  </si>
+  <si>
+    <t>範疇2</t>
+  </si>
+  <si>
+    <t>範疇3</t>
+  </si>
+  <si>
+    <t>固定排放</t>
+  </si>
+  <si>
+    <t>製程排放</t>
+  </si>
+  <si>
+    <t>移動排放</t>
+  </si>
+  <si>
+    <t>逸散排放</t>
+  </si>
+  <si>
+    <t>能源間接排放</t>
+  </si>
+  <si>
+    <t>其他間接排放</t>
+  </si>
+  <si>
+    <t>[類別一總排放]</t>
+  </si>
+  <si>
+    <t>[類別二總排放]</t>
+  </si>
+  <si>
+    <t>[固定排放量]</t>
+  </si>
+  <si>
+    <t>[製程排放量]</t>
+  </si>
+  <si>
+    <t>[移動排放量]</t>
+  </si>
+  <si>
+    <t>[逸散排放量]</t>
+  </si>
+  <si>
+    <t>等級</t>
+  </si>
+  <si>
+    <t>第一級</t>
+  </si>
+  <si>
+    <t>第二級</t>
+  </si>
+  <si>
+    <t>第三級</t>
+  </si>
+  <si>
+    <t>本清冊之總不確定性</t>
+  </si>
+  <si>
+    <t>評分範圍</t>
+  </si>
+  <si>
+    <t>X&lt;10分</t>
+  </si>
+  <si>
+    <t>10分≦X&lt;19分</t>
+  </si>
+  <si>
+    <t>19≦X≦27分</t>
+  </si>
+  <si>
+    <t>[進行評估排放當量]</t>
+  </si>
+  <si>
+    <t>[總排放當量]</t>
+  </si>
+  <si>
+    <t>個數</t>
+  </si>
+  <si>
+    <t>進行不確定性評估之排放量佔總排放量之比例</t>
+  </si>
+  <si>
+    <t>95%信賴區間下限</t>
+  </si>
+  <si>
+    <t>95%信賴區間上限</t>
+  </si>
+  <si>
+    <t>清冊等級總平均分數</t>
+  </si>
+  <si>
+    <t>清冊級別</t>
+  </si>
+  <si>
+    <t>[95下]</t>
+  </si>
+  <si>
+    <t>[95上]</t>
+  </si>
+  <si>
+    <t>公司名稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英文公司名稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顯著性門檻</t>
+  </si>
+  <si>
+    <t>實質性門檻</t>
+  </si>
+  <si>
+    <t>排除門檻</t>
+  </si>
+  <si>
+    <t>氣體別占比
+(％)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>排放當量
+(公噸CO</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>e/年)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排放當量
+(公噸CO2e/年)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>七種溫室氣體年總排放當量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>數據來源名稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>活動數據誤差等級</t>
-  </si>
-  <si>
-    <t>儀器校正等級</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>排放係數誤差等級</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>數據等級評分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>活動數據信賴區間上限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>活動數據信賴區間下限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CO2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CH4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>N2O</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HFCS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PFCS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SF6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NF3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>溫室氣體</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>排放係數</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GWP值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>排放係數不確性上限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>排放係數不確性下限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>單位</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -145,7 +561,21 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="12">
+    <numFmt numFmtId="176" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="&quot; &quot;#,##0.00&quot; &quot;;&quot;-&quot;#,##0.00&quot; &quot;;&quot; -&quot;00&quot; &quot;;&quot; &quot;@&quot; &quot;"/>
+    <numFmt numFmtId="178" formatCode="0&quot; &quot;"/>
+    <numFmt numFmtId="179" formatCode="#,##0.0000&quot; &quot;;[Red]&quot;(&quot;#,##0.0000&quot;)&quot;"/>
+    <numFmt numFmtId="180" formatCode="#,##0&quot; &quot;;[Red]&quot;(&quot;#,##0&quot;)&quot;"/>
+    <numFmt numFmtId="181" formatCode="&quot;+ &quot;0.000%"/>
+    <numFmt numFmtId="182" formatCode="#,##0.000&quot; &quot;;[Red]&quot;(&quot;#,##0.000&quot;)&quot;"/>
+    <numFmt numFmtId="183" formatCode="0.00&quot; &quot;;[Red]&quot;(&quot;0.00&quot;)&quot;"/>
+    <numFmt numFmtId="184" formatCode="#,##0.00000000&quot; &quot;"/>
+    <numFmt numFmtId="185" formatCode="#,##0.0000&quot; &quot;;[Red]&quot;-&quot;#,##0.0000&quot; &quot;"/>
+    <numFmt numFmtId="186" formatCode="#,##0.000&quot; &quot;"/>
+    <numFmt numFmtId="187" formatCode="&quot;- &quot;0.00%"/>
+  </numFmts>
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -161,16 +591,141 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000066"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000080"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="subscript"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFFF"/>
+        <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor rgb="FFFFFF99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFBFBF"/>
+        <bgColor rgb="FFBFBFBF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0C0C0"/>
+        <bgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -178,19 +733,821 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="8" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="8" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="186" fontId="14" fillId="6" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="14" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="8" fillId="6" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="6" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="6" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="14" fillId="6" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="6" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="8" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="5" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="5" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="9" fillId="6" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="9" fillId="6" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="6" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="6" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="9" fillId="6" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="6" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="6" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="9" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="8" fillId="2" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="8" fillId="2" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="31">
+    <cellStyle name="Articles" xfId="28" xr:uid="{00272ED2-673B-4531-BEE6-B54571E56BAA}"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="一般 2" xfId="2" xr:uid="{3D21790F-B7DC-4B24-93C5-CFC980D33EFA}"/>
+    <cellStyle name="一般 2 2" xfId="5" xr:uid="{F1DF68F8-F3A9-4966-8447-EA0564026E56}"/>
+    <cellStyle name="一般 2 3" xfId="6" xr:uid="{A50CBEA4-E4A4-43B4-A3B6-69C7E7C7B43D}"/>
+    <cellStyle name="一般 3" xfId="7" xr:uid="{4C9346D4-FD64-4B84-800E-108FB6D28C4A}"/>
+    <cellStyle name="一般 3 2" xfId="8" xr:uid="{380C8E54-3F0B-41BC-A504-73699F162C1C}"/>
+    <cellStyle name="一般 3 3" xfId="9" xr:uid="{4B985D61-A2D1-4772-A974-A10BB582AAE5}"/>
+    <cellStyle name="一般 3 4" xfId="10" xr:uid="{40717CA1-6E32-4AD5-812B-2755011D70DE}"/>
+    <cellStyle name="一般 4" xfId="11" xr:uid="{D39E5EFC-940E-439C-8DEC-2E8C4F9340B4}"/>
+    <cellStyle name="一般 4 2" xfId="12" xr:uid="{9BD67276-5EDA-4341-8D78-C3BC11BEA094}"/>
+    <cellStyle name="一般 4 3" xfId="13" xr:uid="{07ED1BE8-05D9-4912-B297-A16A1AAD85B7}"/>
+    <cellStyle name="一般 4 4" xfId="14" xr:uid="{B9B6F410-F66B-4862-917C-1477B029F093}"/>
+    <cellStyle name="一般 5" xfId="29" xr:uid="{F11BFF3B-FA6B-487B-8772-F47C86D60785}"/>
+    <cellStyle name="一般 5 2" xfId="15" xr:uid="{70866F3C-3DF3-47FA-BD61-DEFECEEDC235}"/>
+    <cellStyle name="一般 5 3" xfId="16" xr:uid="{557A040C-C779-446C-92A9-35DDFCABEA9A}"/>
+    <cellStyle name="一般 5 4" xfId="17" xr:uid="{2BFC265E-5BD7-447F-B609-B64D5599794A}"/>
+    <cellStyle name="一般 6" xfId="3" xr:uid="{333C986C-CD77-4368-A772-DFB1377FF835}"/>
+    <cellStyle name="一般 6 2" xfId="18" xr:uid="{368B3700-4897-4850-85CB-792FDBDBA397}"/>
+    <cellStyle name="一般 6 3" xfId="19" xr:uid="{13567B56-2263-406E-935F-06AE2AA7080C}"/>
+    <cellStyle name="一般 6 4" xfId="20" xr:uid="{9DC4D337-FFC8-48FD-B37A-E9B65FEEC051}"/>
+    <cellStyle name="一般 7 2" xfId="21" xr:uid="{4318BBF0-033B-4200-9E4B-7134CE592E2C}"/>
+    <cellStyle name="一般 7 3" xfId="22" xr:uid="{B5731845-3A88-453D-953D-0820E510AFED}"/>
+    <cellStyle name="一般 7 4" xfId="23" xr:uid="{0DC35BAA-2553-494F-9E71-A41E58499194}"/>
+    <cellStyle name="一般 8 2" xfId="24" xr:uid="{426C143C-922C-4978-917D-F66A5C0F1EC8}"/>
+    <cellStyle name="一般 9 2" xfId="25" xr:uid="{3E3B8B3B-7558-469A-B252-69CA8695D20D}"/>
+    <cellStyle name="千分位 2" xfId="26" xr:uid="{BDDECD9F-2456-4CD8-AED0-E3DD57B514EC}"/>
+    <cellStyle name="百分比" xfId="1" builtinId="5"/>
+    <cellStyle name="百分比 2" xfId="27" xr:uid="{25AA0438-FA6B-4A3F-8721-EF07F4EE8294}"/>
+    <cellStyle name="百分比 3" xfId="30" xr:uid="{2031A2FA-0120-4667-8F2D-716B4C9E453C}"/>
+    <cellStyle name="百分比 4" xfId="4" xr:uid="{B03EB58B-8907-4FF4-BE51-8C0DC80A1C40}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -203,6 +1560,170 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="表單說明"/>
+      <sheetName val="表一"/>
+      <sheetName val="表二"/>
+      <sheetName val="表三"/>
+      <sheetName val="表四"/>
+      <sheetName val="表五"/>
+      <sheetName val="表六"/>
+      <sheetName val="表七"/>
+      <sheetName val="表八"/>
+      <sheetName val="表九"/>
+      <sheetName val="附表一"/>
+      <sheetName val="附表二"/>
+      <sheetName val="附表三"/>
+      <sheetName val="附表四"/>
+      <sheetName val="附表五"/>
+      <sheetName val="附表六"/>
+      <sheetName val="附表七"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12">
+        <row r="3">
+          <cell r="E3" t="str">
+            <v>臺北市</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="E4" t="str">
+            <v>基隆市</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="E5" t="str">
+            <v>新北市</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="E6" t="str">
+            <v>宜蘭縣</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="E7" t="str">
+            <v>新竹市</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="E8" t="str">
+            <v>新竹縣</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="E9" t="str">
+            <v>桃園市</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="E10" t="str">
+            <v>苗栗縣</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="E11" t="str">
+            <v>臺中市</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="E12" t="str">
+            <v>彰化縣</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="E13" t="str">
+            <v>南投縣</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="E14" t="str">
+            <v>嘉義市</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="E15" t="str">
+            <v>嘉義縣</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="E16" t="str">
+            <v>雲林縣</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="E17" t="str">
+            <v>臺南市</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="E18" t="str">
+            <v>高雄市</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="E19" t="str">
+            <v>南海諸島</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="E20" t="str">
+            <v>澎湖縣</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21" t="str">
+            <v>屏東縣</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="E22" t="str">
+            <v>臺東縣</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="E23" t="str">
+            <v>花蓮縣</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="E24" t="str">
+            <v>金門縣</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="E25" t="str">
+            <v>連江縣</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -521,95 +2042,186 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85949AA3-7B52-4F62-A00B-17B095F1296B}">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="9.06640625" style="8"/>
+    <col min="2" max="2" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.86328125" style="8" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="26.59765625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="5.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.73046875" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.86328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.06640625" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A1" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="70" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="70" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="70" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="71" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="73" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="73" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="70" t="s">
+        <v>104</v>
+      </c>
+      <c r="L1" s="70" t="s">
+        <v>105</v>
+      </c>
+      <c r="M1" s="74" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="63.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="75"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="79"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{FA991008-5E32-4BD8-B284-52242B8A373E}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="依本署溫室氣體盤查登錄指引，實質性門檻為5%。" sqref="L2" xr:uid="{AFDA3520-2363-4EA0-90CB-E7AFDD4525CF}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="依本署溫室氣體盤查登錄指引，排除門檻為0.5%。_x000a_" sqref="M2" xr:uid="{7D8C4C3A-8BE8-4A43-AAE8-2778A1C3D3DC}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="依本署溫室氣體盤查登錄指引，顯著性門檻為3%。" sqref="K2" xr:uid="{9E1BEBC6-75C2-496E-8F14-06404EE0C158}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0B8FD3C-AD7D-41BE-9A0A-3567FBAAC37F}">
   <dimension ref="A1:V1"/>
-  <sheetFormatPr defaultRowHeight="16.149999999999999" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="4.86328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.1328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.1328125" customWidth="1"/>
-    <col min="15" max="15" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.59765625" customWidth="1"/>
-    <col min="17" max="18" width="23.1328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.59765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.59765625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.86328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="4.86328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.1328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.1328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.1328125" style="8" customWidth="1"/>
+    <col min="15" max="15" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.59765625" style="8" customWidth="1"/>
+    <col min="17" max="18" width="23.1328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.1328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.06640625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+      <c r="A1" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="J1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="L1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="69" t="s">
+        <v>111</v>
+      </c>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="P1" s="69" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q1" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="S1" s="69" t="s">
+        <v>112</v>
+      </c>
+      <c r="T1" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="O1" t="s">
-        <v>4</v>
-      </c>
-      <c r="P1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>11</v>
-      </c>
-      <c r="R1" t="s">
-        <v>12</v>
-      </c>
-      <c r="S1" t="s">
+      <c r="U1" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" s="69" t="s">
         <v>8</v>
-      </c>
-      <c r="U1" t="s">
-        <v>9</v>
-      </c>
-      <c r="V1" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -618,51 +2230,629 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AEAC39B-06AD-4425-A509-11D48C173669}">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="16.149999999999999" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.1328125" customWidth="1"/>
-    <col min="7" max="7" width="17.19921875" customWidth="1"/>
-    <col min="8" max="9" width="20.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.86328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.1328125" style="8" customWidth="1"/>
+    <col min="7" max="7" width="17.19921875" style="8" customWidth="1"/>
+    <col min="8" max="9" width="20.86328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.06640625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+      <c r="A1" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="69" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="G1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" t="s">
-        <v>24</v>
-      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A28" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E0EF0D4-F645-42D6-8647-B00483EEB98C}">
+  <dimension ref="A1:M24"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="21.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.86328125" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.265625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.19921875" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.46484375" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.9296875" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34.9296875" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.06640625" style="25"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="59"/>
+      <c r="B1" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="24"/>
+    </row>
+    <row r="2" spans="1:13" ht="17.649999999999999" x14ac:dyDescent="0.45">
+      <c r="A2" s="60"/>
+      <c r="B2" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="J2" s="24"/>
+    </row>
+    <row r="3" spans="1:13" ht="33" x14ac:dyDescent="0.45">
+      <c r="A3" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" s="26" t="e">
+        <f>B3+C3+D3+E3+F3+G3+H3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J3" s="12"/>
+    </row>
+    <row r="4" spans="1:13" ht="31.15" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="31" t="e">
+        <f>B3/$I$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C4" s="31" t="e">
+        <f t="shared" ref="C4:H4" si="0">C3/$I$3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D4" s="31" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E4" s="31" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F4" s="31" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G4" s="31" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H4" s="31" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I4" s="27">
+        <v>1</v>
+      </c>
+      <c r="J4" s="24"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+    </row>
+    <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A7" s="59"/>
+      <c r="B7" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="24"/>
+    </row>
+    <row r="8" spans="1:13" ht="17.649999999999999" x14ac:dyDescent="0.45">
+      <c r="A8" s="60"/>
+      <c r="B8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="24"/>
+    </row>
+    <row r="9" spans="1:13" ht="33" x14ac:dyDescent="0.45">
+      <c r="A9" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="28" t="e">
+        <f>B9+C9+D9+E9+F9+G9+H9</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J9" s="24"/>
+    </row>
+    <row r="10" spans="1:13" ht="31.15" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="31" t="e">
+        <f>B9/$I$9</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C10" s="31" t="e">
+        <f t="shared" ref="C10:H10" si="1">C9/$I$9</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D10" s="31" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E10" s="31" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F10" s="31" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G10" s="31" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H10" s="31" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I10" s="27">
+        <v>1</v>
+      </c>
+      <c r="J10" s="24"/>
+    </row>
+    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A12" s="59"/>
+      <c r="B12" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="42"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A13" s="61"/>
+      <c r="B13" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" s="66" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A14" s="60"/>
+      <c r="B14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="67"/>
+    </row>
+    <row r="15" spans="1:13" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="63" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="43">
+        <v>0</v>
+      </c>
+      <c r="H15" s="47" t="e">
+        <f>B15+F15+G15</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A16" s="60"/>
+      <c r="B16" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="48"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A17" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="51" t="e">
+        <f>B15/$H$15</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="45" t="e">
+        <f>F15/$H$15</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G17" s="45" t="e">
+        <f>G15/$H$15</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H17" s="49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A18" s="35"/>
+      <c r="B18" s="31" t="e">
+        <f>B16/$B$15</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C18" s="31" t="e">
+        <f t="shared" ref="C18:E18" si="2">C16/$B$15</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D18" s="31" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E18" s="31" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="50"/>
+    </row>
+    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="24"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A20" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="42"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="24"/>
+      <c r="F21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H21" s="55" t="s">
+        <v>87</v>
+      </c>
+      <c r="I21" s="56"/>
+    </row>
+    <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="24"/>
+      <c r="F22" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="H22" s="57"/>
+      <c r="I22" s="58"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="24"/>
+      <c r="F23" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="G23" s="39"/>
+      <c r="H23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="18.399999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A24" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="24"/>
+      <c r="F24" s="36" t="e">
+        <f>F22/G22</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G24" s="37"/>
+      <c r="H24" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="I24" s="30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="H21:I22"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/wwwroot/test.xlsx
+++ b/wwwroot/test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Carbon-inventory-platform\wwwroot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FCBEEE5-AD9F-48B1-BC93-B5277F34E7DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4D8293-5EAD-48D3-BF60-D764DE05D50C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" xr2:uid="{B6C6FE3C-00CF-427C-BF72-AD6EBFF9061C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12345" activeTab="2" xr2:uid="{B6C6FE3C-00CF-427C-BF72-AD6EBFF9061C}"/>
   </bookViews>
   <sheets>
     <sheet name="邊界資料" sheetId="4" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="117">
   <si>
     <t>原燃物料</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,18 +68,6 @@
   </si>
   <si>
     <t>CO2排放當量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>儀器校正等級</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>排放係數誤差等級</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>數據等級評分</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -456,9 +444,6 @@
   </si>
   <si>
     <t>19≦X≦27分</t>
-  </si>
-  <si>
-    <t>[進行評估排放當量]</t>
   </si>
   <si>
     <t>[總排放當量]</t>
@@ -553,7 +538,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>活動數據誤差等級</t>
+    <t>GWP版本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[進行評估排放當量]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>數據等級評分(AxBxC)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活動數據誤差等級(A)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>儀器校正等級(B)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排放係數誤差等級(C)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不確定性定量上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不確定性定量下限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CO2排放當量單位</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -687,7 +704,7 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -724,6 +741,12 @@
         <bgColor rgb="FFC0C0C0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="36">
     <border>
@@ -1260,7 +1283,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1363,6 +1386,36 @@
     <xf numFmtId="182" fontId="8" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1453,6 +1506,15 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1466,53 +1528,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2043,7 +2058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85949AA3-7B52-4F62-A00B-17B095F1296B}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.06640625" style="8"/>
@@ -2055,66 +2070,71 @@
     <col min="7" max="7" width="5.33203125" style="8" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="9.73046875" style="8" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.86328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.06640625" style="8"/>
+    <col min="11" max="11" width="7.59765625" style="8" customWidth="1"/>
+    <col min="12" max="13" width="11.86328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.06640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A1" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="70" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A1" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="L1" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="M1" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="N1" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="70" t="s">
-        <v>103</v>
-      </c>
-      <c r="D1" s="70" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="71" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="71" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="72" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="73" t="s">
-        <v>30</v>
-      </c>
-      <c r="J1" s="71" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="70" t="s">
-        <v>104</v>
-      </c>
-      <c r="L1" s="70" t="s">
-        <v>105</v>
-      </c>
-      <c r="M1" s="74" t="s">
-        <v>106</v>
-      </c>
     </row>
-    <row r="2" spans="1:13" ht="63.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="75"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="79"/>
+    <row r="2" spans="1:14" ht="63.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2122,9 +2142,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{FA991008-5E32-4BD8-B284-52242B8A373E}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="依本署溫室氣體盤查登錄指引，實質性門檻為5%。" sqref="L2" xr:uid="{AFDA3520-2363-4EA0-90CB-E7AFDD4525CF}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="依本署溫室氣體盤查登錄指引，排除門檻為0.5%。_x000a_" sqref="M2" xr:uid="{7D8C4C3A-8BE8-4A43-AAE8-2778A1C3D3DC}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="依本署溫室氣體盤查登錄指引，顯著性門檻為3%。" sqref="K2" xr:uid="{9E1BEBC6-75C2-496E-8F14-06404EE0C158}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="依本署溫室氣體盤查登錄指引，實質性門檻為5%。" sqref="M2" xr:uid="{AFDA3520-2363-4EA0-90CB-E7AFDD4525CF}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="依本署溫室氣體盤查登錄指引，排除門檻為0.5%。_x000a_" sqref="N2" xr:uid="{7D8C4C3A-8BE8-4A43-AAE8-2778A1C3D3DC}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="依本署溫室氣體盤查登錄指引，顯著性門檻為3%。" sqref="L2" xr:uid="{9E1BEBC6-75C2-496E-8F14-06404EE0C158}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2132,96 +2152,108 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0B8FD3C-AD7D-41BE-9A0A-3567FBAAC37F}">
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.86328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="4.86328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.1328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.796875" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.1328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.1328125" style="8" customWidth="1"/>
-    <col min="15" max="15" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.59765625" style="8" customWidth="1"/>
-    <col min="17" max="18" width="23.1328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.1328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.1328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.06640625" style="8"/>
+    <col min="1" max="1" width="5.46484375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.73046875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.73046875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.53125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.9296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.86328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.9296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.265625" style="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.1328125" style="8" customWidth="1"/>
+    <col min="16" max="16" width="9.73046875" style="8" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.46484375" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="23.265625" style="8" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.9296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.265625" style="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="21.796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="22.796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="18.73046875" style="8" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.06640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A1" s="69" t="s">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.45">
+      <c r="A1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="69" t="s">
+      <c r="C1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="69" t="s">
+      <c r="D1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="69" t="s">
+      <c r="E1" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="69" t="s">
+      <c r="I1" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="69" t="s">
+      <c r="J1" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="69" t="s">
+      <c r="K1" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="69" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="69" t="s">
+      <c r="L1" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="69" t="s">
+      <c r="M1" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="N1" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q1" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="R1" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="S1" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="T1" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69" t="s">
-        <v>4</v>
-      </c>
-      <c r="P1" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q1" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="S1" s="69" t="s">
+      <c r="U1" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="T1" s="69" t="s">
-        <v>6</v>
-      </c>
-      <c r="U1" s="69" t="s">
-        <v>7</v>
-      </c>
-      <c r="V1" s="69" t="s">
-        <v>8</v>
+      <c r="V1" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="W1" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="X1" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y1" s="34" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -2246,32 +2278,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="69" t="s">
+      <c r="C1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="69" t="s">
+      <c r="D1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="69" t="s">
+      <c r="E1" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="69" t="s">
+      <c r="I1" s="34" t="s">
         <v>19</v>
-      </c>
-      <c r="H1" s="69" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="69" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.45">
@@ -2302,71 +2334,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="59"/>
-      <c r="B1" s="80" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="82"/>
+      <c r="A1" s="68"/>
+      <c r="B1" s="73" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="75"/>
       <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:13" ht="17.649999999999999" x14ac:dyDescent="0.45">
-      <c r="A2" s="60"/>
+      <c r="A2" s="69"/>
       <c r="B2" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>53</v>
-      </c>
       <c r="I2" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J2" s="24"/>
     </row>
     <row r="3" spans="1:13" ht="33" x14ac:dyDescent="0.45">
       <c r="A3" s="33" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B3" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="F3" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>60</v>
       </c>
       <c r="I3" s="26" t="e">
         <f>B3+C3+D3+E3+F3+G3+H3</f>
@@ -2376,7 +2408,7 @@
     </row>
     <row r="4" spans="1:13" ht="31.15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="32" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B4" s="31" t="e">
         <f>B3/$I$3</f>
@@ -2442,71 +2474,71 @@
       <c r="M6" s="24"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A7" s="59"/>
-      <c r="B7" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="54"/>
+      <c r="A7" s="68"/>
+      <c r="B7" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="63"/>
       <c r="J7" s="24"/>
     </row>
     <row r="8" spans="1:13" ht="17.649999999999999" x14ac:dyDescent="0.45">
-      <c r="A8" s="60"/>
+      <c r="A8" s="69"/>
       <c r="B8" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C8" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="16" t="s">
+      <c r="I8" s="7" t="s">
         <v>32</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="J8" s="24"/>
     </row>
     <row r="9" spans="1:13" ht="33" x14ac:dyDescent="0.45">
       <c r="A9" s="33" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B9" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="F9" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="G9" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="H9" s="11" t="s">
         <v>64</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>67</v>
       </c>
       <c r="I9" s="28" t="e">
         <f>B9+C9+D9+E9+F9+G9+H9</f>
@@ -2516,7 +2548,7 @@
     </row>
     <row r="10" spans="1:13" ht="31.15" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="32" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B10" s="31" t="e">
         <f>B9/$I$9</f>
@@ -2564,121 +2596,121 @@
       <c r="J11" s="24"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A12" s="59"/>
-      <c r="B12" s="68" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="42"/>
+      <c r="A12" s="68"/>
+      <c r="B12" s="80" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="50"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="50"/>
+      <c r="H12" s="51"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A13" s="61"/>
-      <c r="B13" s="64" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="65"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="39"/>
+      <c r="A13" s="70"/>
+      <c r="B13" s="76" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="77"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="48"/>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H13" s="66" t="s">
-        <v>48</v>
+        <v>67</v>
+      </c>
+      <c r="H13" s="78" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A14" s="60"/>
+      <c r="A14" s="69"/>
       <c r="B14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H14" s="67"/>
+      <c r="H14" s="79"/>
     </row>
     <row r="15" spans="1:13" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="63" t="s">
-        <v>109</v>
-      </c>
-      <c r="B15" s="62" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="43" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" s="43">
+      <c r="A15" s="72" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="52" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="52">
         <v>0</v>
       </c>
-      <c r="H15" s="47" t="e">
+      <c r="H15" s="56" t="e">
         <f>B15+F15+G15</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A16" s="60"/>
+      <c r="A16" s="69"/>
       <c r="B16" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="48"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="57"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A17" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="B17" s="51" t="e">
+      <c r="A17" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="60" t="e">
         <f>B15/$H$15</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="45" t="e">
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="54" t="e">
         <f>F15/$H$15</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G17" s="45" t="e">
+      <c r="G17" s="54" t="e">
         <f>G15/$H$15</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H17" s="49">
+      <c r="H17" s="58">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="35"/>
+      <c r="A18" s="44"/>
       <c r="B18" s="31" t="e">
         <f>B16/$B$15</f>
         <v>#VALUE!</v>
@@ -2695,9 +2727,9 @@
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="50"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="59"/>
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A19" s="24"/>
@@ -2713,117 +2745,117 @@
       <c r="K19" s="24"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A20" s="52" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="54"/>
+      <c r="A20" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="62"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="63"/>
       <c r="E20" s="19"/>
-      <c r="F20" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="42"/>
+      <c r="F20" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="50"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="51"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>86</v>
       </c>
       <c r="E21" s="24"/>
       <c r="F21" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H21" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="I21" s="56"/>
+        <v>34</v>
+      </c>
+      <c r="H21" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="I21" s="65"/>
     </row>
     <row r="22" spans="1:11" ht="18" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>91</v>
       </c>
       <c r="E22" s="24"/>
       <c r="F22" s="20" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="H22" s="57"/>
-      <c r="I22" s="58"/>
+        <v>89</v>
+      </c>
+      <c r="H22" s="66"/>
+      <c r="I22" s="67"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E23" s="24"/>
-      <c r="F23" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="G23" s="39"/>
+      <c r="F23" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="48"/>
       <c r="H23" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="18.399999999999999" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A24" s="17" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E24" s="24"/>
-      <c r="F24" s="36" t="e">
+      <c r="F24" s="45" t="e">
         <f>F22/G22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G24" s="37"/>
+      <c r="G24" s="46"/>
       <c r="H24" s="29" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I24" s="30" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
